--- a/docs/downloads/经营分_津河省区__津东片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__津东片区_2026-10-18.xlsx
@@ -877,7 +877,7 @@
         <v>68</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1375,29 +1375,29 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6845044439950411791</t>
+          <t>6763895812595468296</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津东丽开发区地铁站店</t>
+          <t>希岸酒店天津滨江道和平路地铁站劝业场店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津东丽开发区地铁站店)</t>
+          <t>希岸酒店(天津滨江道和平路地铁站劝业场店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>87</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1463,22 +1463,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7276268799819515956</t>
+          <t>6845044439950411791</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津华明滨海国际机场店</t>
+          <t>麗枫酒店·天津东丽开发区地铁站店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津华明滨海国际机场店)</t>
+          <t>麗枫酒店(天津东丽开发区地铁站店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1551,22 +1551,22 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6738219457916733453</t>
+          <t>7276268799819515956</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津大悦城鼓楼地铁站店</t>
+          <t>麗枫酒店·天津华明滨海国际机场店</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津大悦城鼓楼地铁站店)</t>
+          <t>麗枫酒店(天津华明滨海国际机场店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1639,26 +1639,26 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6601175799364061188</t>
+          <t>6738219457916733453</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7天优品（天津成林道万新村武警医院店）</t>
+          <t>麗枫酒店·天津大悦城鼓楼地铁站店</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7天优品酒店(天津成林道万新村武警医院店)</t>
+          <t>麗枫酒店(天津大悦城鼓楼地铁站店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1675,7 +1675,7 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
@@ -1687,7 +1687,7 @@
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1727,22 +1727,22 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6601136810775021582</t>
+          <t>6601175799364061188</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IU酒店·天津机场空港经济区店</t>
+          <t>7天优品（天津成林道万新村武警医院店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>iu酒店(天津机场空港经济区店)</t>
+          <t>7天优品酒店(天津成林道万新村武警医院店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1763,7 +1763,7 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
@@ -1775,7 +1775,7 @@
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6870867024571009031</t>
+          <t>6601136810775021582</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津滨海国际机场武警医院店）</t>
+          <t>IU酒店·天津机场空港经济区店</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津滨海国际机场武警医院店)</t>
+          <t>iu酒店(天津机场空港经济区店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
@@ -1863,7 +1863,7 @@
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1903,17 +1903,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6763895812595468296</t>
+          <t>6824286894663206920</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>希岸酒店天津滨江道和平路地铁站劝业场店</t>
+          <t>喆啡酒店（天津古文化街鼓楼地铁站店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>希岸酒店(天津滨江道和平路地铁站劝业场店)</t>
+          <t>喆啡酒店(天津古文化街鼓楼地铁站店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>92</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
@@ -1991,17 +1991,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7118338141840214028</t>
+          <t>6870867024571009031</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津海光寺眼科医院店）</t>
+          <t>喆啡酒店（天津滨海国际机场武警医院店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津海光寺眼科医院店)</t>
+          <t>喆啡酒店(天津滨海国际机场武警医院店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2010,18 +2010,18 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I17" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6886081243822491661</t>
+          <t>7118338141840214028</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店（天津古文化街鼓楼地铁站店）</t>
+          <t>喆啡酒店（天津海光寺眼科医院店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(天津大悦城鼓楼地铁站店)</t>
+          <t>喆啡酒店(天津海光寺眼科医院店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2101,7 +2101,7 @@
         <v>93</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2167,17 +2167,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7048813080796465159</t>
+          <t>6886081243822491661</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7天优品（天津北方五金城店）</t>
+          <t>希岸·轻雅酒店（天津古文化街鼓楼地铁站店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7天优品酒店(北方五金城店)</t>
+          <t>希岸·轻雅酒店(天津大悦城鼓楼地铁站店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2186,30 +2186,30 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>10</v>
       </c>
       <c r="M19" t="n">
+        <v>22</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" t="n">
         <v>25</v>
-      </c>
-      <c r="N19" t="n">
-        <v>30</v>
-      </c>
-      <c r="O19" t="n">
-        <v>20</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
@@ -2255,22 +2255,22 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7506790632631830547</t>
+          <t>7048813080796465159</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>非繁城品酒店(天津空港滨海国际机场店)</t>
+          <t>7天优品（天津北方五金城店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>非繁城品酒店(天津空港滨海国际机场店)</t>
+          <t>7天优品酒店(北方五金城店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2297,13 +2297,13 @@
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2343,37 +2343,37 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7132466961895819298</t>
+          <t>7506790632631830547</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>麗枫酒店天津万科民和巷店</t>
+          <t>非繁城品酒店(天津空港滨海国际机场店)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津东丽万科民和巷店)</t>
+          <t>非繁城品酒店(天津空港滨海国际机场店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
         <v>10</v>
@@ -2391,7 +2391,7 @@
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2431,17 +2431,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6622218143370577924</t>
+          <t>7132466961895819298</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>维也纳酒店天津海光寺眼科医院店</t>
+          <t>麗枫酒店天津万科民和巷店</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津海光寺眼科医院店)</t>
+          <t>麗枫酒店(天津东丽万科民和巷店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2450,24 +2450,24 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6601138246594332675</t>
+          <t>6622218143370577924</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津机场文会路店）</t>
+          <t>维也纳酒店天津海光寺眼科医院店</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津机场华明二店)</t>
+          <t>维也纳酒店(天津海光寺眼科医院店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2541,11 +2541,11 @@
         <v>97</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2561,13 +2561,13 @@
         <v>30</v>
       </c>
       <c r="O23" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P23" t="n">
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R23" t="n">
         <v>30</v>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6824286894663206920</t>
+          <t>6601138246594332675</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津古文化街鼓楼地铁站店）</t>
+          <t>维也纳酒店（天津机场文会路店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津古文化街鼓楼地铁站店)</t>
+          <t>维也纳酒店(天津机场华明二店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2626,14 +2626,14 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2643,19 +2643,19 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P24" t="n">
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2717,7 +2717,7 @@
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
